--- a/Team-Data/2011-12/4-11-2011-12.xlsx
+++ b/Team-Data/2011-12/4-11-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2" t="n">
         <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.586</v>
+        <v>0.596</v>
       </c>
       <c r="H2" t="n">
         <v>49.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J2" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L2" t="n">
         <v>7.2</v>
@@ -691,25 +758,25 @@
         <v>19.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.366</v>
+        <v>0.371</v>
       </c>
       <c r="O2" t="n">
         <v>15.3</v>
       </c>
       <c r="P2" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0.736</v>
       </c>
       <c r="R2" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S2" t="n">
         <v>31.1</v>
       </c>
       <c r="T2" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U2" t="n">
         <v>22.1</v>
@@ -718,7 +785,7 @@
         <v>13.9</v>
       </c>
       <c r="W2" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
@@ -730,31 +797,31 @@
         <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ2" t="n">
         <v>18</v>
@@ -763,13 +830,13 @@
         <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM2" t="n">
         <v>15</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
         <v>26</v>
@@ -784,7 +851,7 @@
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -802,7 +869,7 @@
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -814,7 +881,7 @@
         <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
         <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.586</v>
+        <v>0.579</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
@@ -861,10 +928,10 @@
         <v>35.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L3" t="n">
         <v>5.5</v>
@@ -873,31 +940,31 @@
         <v>14.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="O3" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P3" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>38.9</v>
+        <v>38.6</v>
       </c>
       <c r="U3" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W3" t="n">
         <v>7.3</v>
@@ -909,34 +976,34 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA3" t="n">
         <v>18.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,7 +1012,7 @@
         <v>5</v>
       </c>
       <c r="AL3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM3" t="n">
         <v>24</v>
@@ -954,10 +1021,10 @@
         <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>4</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -975,19 +1042,19 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>19</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-13.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1145,7 +1212,7 @@
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1306,7 +1373,7 @@
         <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1351,7 +1418,7 @@
         <v>19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K6" t="n">
         <v>0.423</v>
@@ -1416,19 +1483,19 @@
         <v>6.9</v>
       </c>
       <c r="M6" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.351</v>
+        <v>0.355</v>
       </c>
       <c r="O6" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.711</v>
+        <v>0.71</v>
       </c>
       <c r="R6" t="n">
         <v>13</v>
@@ -1440,7 +1507,7 @@
         <v>42.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V6" t="n">
         <v>15.3</v>
@@ -1458,34 +1525,34 @@
         <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="AC6" t="n">
         <v>-6</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
         <v>25</v>
       </c>
       <c r="AH6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
@@ -1518,13 +1585,13 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -1649,16 +1716,16 @@
         <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>8</v>
@@ -1682,13 +1749,13 @@
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
@@ -1697,7 +1764,7 @@
         <v>2</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU7" t="n">
         <v>15</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
         <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.552</v>
+        <v>0.544</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
@@ -1774,16 +1841,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.329</v>
+        <v>0.327</v>
       </c>
       <c r="O8" t="n">
         <v>20.2</v>
@@ -1792,25 +1859,25 @@
         <v>27.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.736</v>
+        <v>0.737</v>
       </c>
       <c r="R8" t="n">
         <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T8" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W8" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>5.1</v>
@@ -1819,28 +1886,28 @@
         <v>6.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
         <v>22.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.7</v>
+        <v>103.5</v>
       </c>
       <c r="AC8" t="n">
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1849,10 +1916,10 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>16</v>
@@ -1879,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -1888,7 +1955,7 @@
         <v>27</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
@@ -2055,7 +2122,7 @@
         <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2079,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>0.386</v>
+        <v>0.393</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J10" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L10" t="n">
         <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.389</v>
+        <v>0.388</v>
       </c>
       <c r="O10" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="P10" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R10" t="n">
         <v>9.699999999999999</v>
@@ -2165,7 +2232,7 @@
         <v>29.3</v>
       </c>
       <c r="T10" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U10" t="n">
         <v>22.3</v>
@@ -2189,13 +2256,13 @@
         <v>16.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2207,16 +2274,16 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2252,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" t="n">
         <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.552</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J11" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.452</v>
+        <v>0.454</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M11" t="n">
         <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O11" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P11" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="R11" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S11" t="n">
         <v>30.5</v>
       </c>
       <c r="T11" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U11" t="n">
         <v>21.2</v>
       </c>
       <c r="V11" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X11" t="n">
         <v>4.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z11" t="n">
         <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>12</v>
@@ -2398,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="AK11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
         <v>12</v>
@@ -2407,13 +2474,13 @@
         <v>17</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
@@ -2428,16 +2495,16 @@
         <v>16</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
         <v>20</v>
@@ -2446,7 +2513,7 @@
         <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.621</v>
+        <v>0.614</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2505,19 +2572,19 @@
         <v>0.44</v>
       </c>
       <c r="L12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M12" t="n">
         <v>15.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O12" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P12" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0.779</v>
@@ -2526,40 +2593,40 @@
         <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T12" t="n">
         <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="V12" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W12" t="n">
         <v>7.8</v>
       </c>
       <c r="X12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
         <v>21.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC12" t="n">
         <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
         <v>23</v>
@@ -2589,16 +2656,16 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
         <v>10</v>
@@ -2607,7 +2674,7 @@
         <v>11</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
         <v>30</v>
@@ -2619,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2631,7 +2698,7 @@
         <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -2663,22 +2730,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F13" t="n">
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.603</v>
+        <v>0.596</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J13" t="n">
         <v>81.5</v>
@@ -2690,7 +2757,7 @@
         <v>7.6</v>
       </c>
       <c r="M13" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N13" t="n">
         <v>0.349</v>
@@ -2702,7 +2769,7 @@
         <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="R13" t="n">
         <v>12.2</v>
@@ -2711,7 +2778,7 @@
         <v>29.6</v>
       </c>
       <c r="T13" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U13" t="n">
         <v>21.1</v>
@@ -2720,13 +2787,13 @@
         <v>13.4</v>
       </c>
       <c r="W13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X13" t="n">
         <v>4.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" t="n">
         <v>21.2</v>
@@ -2735,13 +2802,13 @@
         <v>21.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="AC13" t="n">
         <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2753,16 +2820,16 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ13" t="n">
         <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL13" t="n">
         <v>5</v>
@@ -2774,7 +2841,7 @@
         <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -2804,7 +2871,7 @@
         <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ13" t="n">
         <v>24</v>
@@ -2813,10 +2880,10 @@
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -2845,55 +2912,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H14" t="n">
         <v>48.5</v>
       </c>
       <c r="I14" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J14" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="K14" t="n">
         <v>0.457</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
-        <v>0.321</v>
+        <v>0.318</v>
       </c>
       <c r="O14" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R14" t="n">
         <v>11.9</v>
       </c>
       <c r="S14" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="T14" t="n">
-        <v>46.2</v>
+        <v>45.9</v>
       </c>
       <c r="U14" t="n">
         <v>22</v>
@@ -2902,28 +2969,28 @@
         <v>15.1</v>
       </c>
       <c r="W14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X14" t="n">
         <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB14" t="n">
         <v>96.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2944,16 +3011,16 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM14" t="n">
         <v>18</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
@@ -2962,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2977,7 +3044,7 @@
         <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
@@ -2989,13 +3056,13 @@
         <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
         <v>11</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
         <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>0.596</v>
+        <v>0.589</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J15" t="n">
         <v>82.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L15" t="n">
         <v>4.1</v>
@@ -3057,19 +3124,19 @@
         <v>12.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="O15" t="n">
         <v>17.3</v>
       </c>
       <c r="P15" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S15" t="n">
         <v>29.8</v>
@@ -3090,7 +3157,7 @@
         <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z15" t="n">
         <v>19.9</v>
@@ -3099,28 +3166,28 @@
         <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF15" t="n">
         <v>7</v>
       </c>
       <c r="AG15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI15" t="n">
         <v>14</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>9</v>
@@ -3150,7 +3217,7 @@
         <v>6</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
@@ -3159,7 +3226,7 @@
         <v>23</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
@@ -3168,19 +3235,19 @@
         <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ15" t="n">
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -3287,22 +3354,22 @@
         <v>6.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -3317,19 +3384,19 @@
         <v>23</v>
       </c>
       <c r="AN16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO16" t="n">
         <v>5</v>
       </c>
-      <c r="AO16" t="n">
-        <v>4</v>
-      </c>
       <c r="AP16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
         <v>10</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -3391,34 +3458,34 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" t="n">
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.483</v>
+        <v>0.491</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J17" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L17" t="n">
         <v>6.8</v>
       </c>
       <c r="M17" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N17" t="n">
         <v>0.347</v>
@@ -3430,7 +3497,7 @@
         <v>20.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.777</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
         <v>12.5</v>
@@ -3463,13 +3530,13 @@
         <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3496,10 +3563,10 @@
         <v>14</v>
       </c>
       <c r="AM17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
         <v>17</v>
@@ -3508,7 +3575,7 @@
         <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR17" t="n">
         <v>5</v>
@@ -3523,19 +3590,19 @@
         <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW17" t="n">
         <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>0.424</v>
+        <v>0.431</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J18" t="n">
         <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L18" t="n">
         <v>7.3</v>
@@ -3606,25 +3673,25 @@
         <v>0.337</v>
       </c>
       <c r="O18" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="P18" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R18" t="n">
         <v>12.4</v>
       </c>
       <c r="S18" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T18" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U18" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V18" t="n">
         <v>15.3</v>
@@ -3633,25 +3700,25 @@
         <v>6.9</v>
       </c>
       <c r="X18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
         <v>5.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>21</v>
@@ -3663,7 +3730,7 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
         <v>20</v>
@@ -3675,7 +3742,7 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
@@ -3684,19 +3751,19 @@
         <v>21</v>
       </c>
       <c r="AO18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP18" t="n">
         <v>5</v>
       </c>
-      <c r="AP18" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>3</v>
@@ -3705,16 +3772,16 @@
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3872,7 +3939,7 @@
         <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>8</v>
@@ -3887,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>16</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -3937,61 +4004,61 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.276</v>
+        <v>0.263</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J20" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L20" t="n">
         <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O20" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="P20" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R20" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U20" t="n">
         <v>20.8</v>
       </c>
       <c r="V20" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W20" t="n">
         <v>7.3</v>
@@ -4003,19 +4070,19 @@
         <v>5.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>89.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4.5</v>
+        <v>-4.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,13 +4094,13 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
@@ -4045,13 +4112,13 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
         <v>12</v>
@@ -4060,7 +4127,7 @@
         <v>17</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4075,7 +4142,7 @@
         <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -4119,46 +4186,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
         <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>0.517</v>
+        <v>0.509</v>
       </c>
       <c r="H21" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J21" t="n">
         <v>81</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L21" t="n">
         <v>7.3</v>
       </c>
       <c r="M21" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.32</v>
+        <v>0.319</v>
       </c>
       <c r="O21" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P21" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R21" t="n">
         <v>11.7</v>
@@ -4170,7 +4237,7 @@
         <v>42.5</v>
       </c>
       <c r="U21" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V21" t="n">
         <v>16.4</v>
@@ -4179,7 +4246,7 @@
         <v>9.5</v>
       </c>
       <c r="X21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
         <v>5</v>
@@ -4191,25 +4258,25 @@
         <v>22.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.3</v>
+        <v>97</v>
       </c>
       <c r="AC21" t="n">
         <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF21" t="n">
         <v>17</v>
       </c>
-      <c r="AF21" t="n">
-        <v>16</v>
-      </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4221,13 +4288,13 @@
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
@@ -4236,7 +4303,7 @@
         <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR21" t="n">
         <v>14</v>
@@ -4260,7 +4327,7 @@
         <v>25</v>
       </c>
       <c r="AY21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -4301,55 +4368,55 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" t="n">
         <v>42</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.724</v>
+        <v>0.737</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J22" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L22" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.36</v>
+        <v>0.357</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="P22" t="n">
         <v>26.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.802</v>
+        <v>0.801</v>
       </c>
       <c r="R22" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S22" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T22" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U22" t="n">
         <v>18.5</v>
@@ -4358,13 +4425,13 @@
         <v>16.4</v>
       </c>
       <c r="W22" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X22" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z22" t="n">
         <v>20.2</v>
@@ -4373,13 +4440,13 @@
         <v>19.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4403,10 +4470,10 @@
         <v>1</v>
       </c>
       <c r="AL22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN22" t="n">
         <v>11</v>
@@ -4415,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
@@ -4427,7 +4494,7 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>28</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -4561,19 +4628,19 @@
         <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI23" t="n">
         <v>29</v>
@@ -4582,7 +4649,7 @@
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4606,10 +4673,10 @@
         <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
@@ -4621,7 +4688,7 @@
         <v>26</v>
       </c>
       <c r="AX23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
@@ -4630,13 +4697,13 @@
         <v>4</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -4665,37 +4732,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
         <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>0.534</v>
+        <v>0.526</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J24" t="n">
-        <v>83.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M24" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O24" t="n">
         <v>13.2</v>
@@ -4704,25 +4771,25 @@
         <v>17.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R24" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S24" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T24" t="n">
         <v>43.1</v>
       </c>
       <c r="U24" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V24" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="W24" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>5.1</v>
@@ -4731,7 +4798,7 @@
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AA24" t="n">
         <v>16.1</v>
@@ -4740,10 +4807,10 @@
         <v>93.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4758,7 +4825,7 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
         <v>5</v>
@@ -4767,13 +4834,13 @@
         <v>15</v>
       </c>
       <c r="AL24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4782,19 +4849,19 @@
         <v>30</v>
       </c>
       <c r="AQ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
@@ -4803,10 +4870,10 @@
         <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -4847,43 +4914,43 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E25" t="n">
         <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.517</v>
+        <v>0.526</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J25" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0.757</v>
@@ -4892,10 +4959,10 @@
         <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="T25" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U25" t="n">
         <v>22.7</v>
@@ -4904,49 +4971,49 @@
         <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA25" t="n">
         <v>19.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4955,34 +5022,34 @@
         <v>13</v>
       </c>
       <c r="AN25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
         <v>5</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX25" t="n">
         <v>5</v>
@@ -4994,13 +5061,13 @@
         <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
         <v>11</v>
       </c>
       <c r="BC25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -5029,55 +5096,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" t="n">
         <v>31</v>
       </c>
       <c r="G26" t="n">
-        <v>0.475</v>
+        <v>0.466</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.445</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O26" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P26" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S26" t="n">
         <v>29.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U26" t="n">
         <v>20.6</v>
@@ -5095,22 +5162,22 @@
         <v>4.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
         <v>20</v>
@@ -5119,10 +5186,10 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
         <v>13</v>
@@ -5137,13 +5204,13 @@
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
         <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
@@ -5152,7 +5219,7 @@
         <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5161,10 +5228,10 @@
         <v>17</v>
       </c>
       <c r="AV26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX26" t="n">
         <v>16</v>
@@ -5173,13 +5240,13 @@
         <v>8</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>0.322</v>
+        <v>0.328</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5229,7 +5296,7 @@
         <v>37.2</v>
       </c>
       <c r="J27" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="K27" t="n">
         <v>0.432</v>
@@ -5241,7 +5308,7 @@
         <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>0.314</v>
+        <v>0.313</v>
       </c>
       <c r="O27" t="n">
         <v>17.6</v>
@@ -5256,19 +5323,19 @@
         <v>13.6</v>
       </c>
       <c r="S27" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U27" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V27" t="n">
         <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X27" t="n">
         <v>4.8</v>
@@ -5277,10 +5344,10 @@
         <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB27" t="n">
         <v>98.2</v>
@@ -5289,7 +5356,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5316,7 +5383,7 @@
         <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN27" t="n">
         <v>28</v>
@@ -5334,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT27" t="n">
         <v>5</v>
@@ -5343,19 +5410,19 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW27" t="n">
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA27" t="n">
         <v>9</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
         <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.714</v>
+        <v>0.727</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
       </c>
       <c r="I28" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="J28" t="n">
         <v>82.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.47</v>
+        <v>0.472</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.388</v>
+        <v>0.385</v>
       </c>
       <c r="O28" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R28" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S28" t="n">
         <v>32.3</v>
       </c>
       <c r="T28" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="U28" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V28" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W28" t="n">
         <v>7.3</v>
@@ -5462,16 +5529,16 @@
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.7</v>
+        <v>102</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,7 +5550,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5492,7 +5559,7 @@
         <v>6</v>
       </c>
       <c r="AK28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL28" t="n">
         <v>2</v>
@@ -5504,7 +5571,7 @@
         <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>21</v>
@@ -5513,13 +5580,13 @@
         <v>25</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS28" t="n">
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5528,7 +5595,7 @@
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX28" t="n">
         <v>24</v>
@@ -5540,7 +5607,7 @@
         <v>3</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="J29" t="n">
         <v>78.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
         <v>5.6</v>
@@ -5605,76 +5672,76 @@
         <v>16.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O29" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P29" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
       </c>
       <c r="S29" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T29" t="n">
         <v>41.6</v>
       </c>
       <c r="U29" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V29" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W29" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X29" t="n">
         <v>4.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.3</v>
+        <v>91.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
       </c>
       <c r="AF29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
         <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5689,28 +5756,28 @@
         <v>15</v>
       </c>
       <c r="AP29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ29" t="n">
         <v>11</v>
       </c>
       <c r="AR29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV29" t="n">
         <v>19</v>
       </c>
-      <c r="AU29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>18</v>
-      </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="H30" t="n">
         <v>48.8</v>
       </c>
       <c r="I30" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J30" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L30" t="n">
         <v>3.9</v>
@@ -5787,25 +5854,25 @@
         <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.312</v>
+        <v>0.309</v>
       </c>
       <c r="O30" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P30" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0.75</v>
       </c>
       <c r="R30" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S30" t="n">
         <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U30" t="n">
         <v>21.7</v>
@@ -5814,7 +5881,7 @@
         <v>14.2</v>
       </c>
       <c r="W30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
         <v>5.8</v>
@@ -5829,22 +5896,22 @@
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
@@ -5880,13 +5947,13 @@
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT30" t="n">
         <v>4</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV30" t="n">
         <v>11</v>
@@ -5910,7 +5977,7 @@
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
         <v>18</v>
@@ -6041,7 +6108,7 @@
         <v>23</v>
       </c>
       <c r="AL31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM31" t="n">
         <v>21</v>
@@ -6050,7 +6117,7 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
@@ -6062,10 +6129,10 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6080,13 +6147,13 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>26</v>
       </c>
       <c r="BA31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-11-2011-12</t>
+          <t>2012-04-11</t>
         </is>
       </c>
     </row>
